--- a/entre_mundos_app/data/pacote.xlsx
+++ b/entre_mundos_app/data/pacote.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,6 +475,94 @@
       </c>
       <c r="F2" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Lote 1 - com desconto de 5% pix</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2607.75</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Lote early birds - 5% no pix</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2607.75</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Lote Early Birds - Parcelado no cartão</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2536.16</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Lote 1 - á vista cheio</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2745</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
